--- a/CHICAGO DEEP DISH PIZZA/Existencias_Diarias_Chicago.xlsx
+++ b/CHICAGO DEEP DISH PIZZA/Existencias_Diarias_Chicago.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Existencias diarias" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Existencias diarias'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Existencias diarias'!$1:$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +30,15 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <i val="1"/>
+      <color rgb="005A1E12"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="18"/>
+      <sz val="17"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -77,6 +84,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="005A1E12"/>
       </patternFill>
     </fill>
@@ -98,11 +110,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F3D9B4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -151,34 +158,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -256,6 +266,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1314450" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -547,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D140"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -556,1390 +596,1399 @@
     <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="56" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">      Control diario de existencias</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
           <t>CHICAGO DEEP DISH PIZZA</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Control diario de existencias y pedido de insumos</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>Control diario de existencias y requisición de insumos</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>Fecha:</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Registró (Jefe de cocina):</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Instrucciones: registra diariamente la EXISTENCIA / STOCK (porciones o cantidad disponible) de cada producto y anota en REQUISICIÓN la cantidad que se necesita pedir. Usa Observaciones para notas (caducidad, faltantes, etc.).</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Existencia / Stock</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Requisición</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>VERDURA</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Ajo</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="11" t="n"/>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="12" t="n"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Albahaca</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="13" t="n"/>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Apio</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="11" t="n"/>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="12" t="n"/>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Cebolla</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="13" t="n"/>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="14" t="n"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Cebolla Morada</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="11" t="n"/>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Champiñón</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="13" t="n"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="14" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Chile de Árbol</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="11" t="n"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="12" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Chile Serrano</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="13" t="n"/>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Chile Guajillo</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="11" t="n"/>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="12" t="n"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Chile Jalapeño</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Chile Morita</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="11" t="n"/>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="12" t="n"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Coliflor</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="13" t="n"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Espárragos</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="11" t="n"/>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="12" t="n"/>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Espinaca</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="13" t="n"/>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Huevo</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="11" t="n"/>
-    </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="12" t="n"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Jitomate</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="13" t="n"/>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="14" t="n"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Lechuga Orejona</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="11" t="n"/>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="12" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Lechuga Sangría</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="13" t="n"/>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="14" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Limón</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="11" t="n"/>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="12" t="n"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Manzana</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="13" t="n"/>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="14" t="n"/>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Pimiento</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="11" t="n"/>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="12" t="n"/>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>Orégano</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="13" t="n"/>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="14" t="n"/>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Uva</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="11" t="n"/>
-    </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="12" t="n"/>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Zanahoria</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="13" t="n"/>
-    </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="9" t="inlineStr"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="11" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="14" t="n"/>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="12" t="inlineStr"/>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="13" t="n"/>
-    </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="13" t="inlineStr"/>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="14" t="n"/>
+    </row>
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>CARNES Y CONGELADOS</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-    </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Alitas</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="11" t="n"/>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="12" t="n"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>BBQ</t>
         </is>
       </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="13" t="n"/>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="14" t="n"/>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Boneless</t>
         </is>
       </c>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="11" t="n"/>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="12" t="n"/>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>Búfalo</t>
         </is>
       </c>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="13" t="n"/>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="14" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Calamares</t>
         </is>
       </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="11" t="n"/>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="12" t="n"/>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>Camarón</t>
         </is>
       </c>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="13" t="n"/>
-    </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="14" t="n"/>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Carne Molida</t>
         </is>
       </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="11" t="n"/>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="12" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>Chistorra</t>
         </is>
       </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="13" t="n"/>
-    </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="14" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Dedos de Queso</t>
         </is>
       </c>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="11" t="n"/>
-    </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="12" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>Pan</t>
         </is>
       </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="13" t="n"/>
-    </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>Nieve de Vainilla</t>
         </is>
       </c>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="11" t="n"/>
-    </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="12" t="n"/>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>Papas a la Francesa</t>
         </is>
       </c>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="13" t="n"/>
-    </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="14" t="n"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Pepperoni</t>
         </is>
       </c>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="10" t="n"/>
-      <c r="D47" s="11" t="n"/>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="12" t="n"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>Ranch</t>
         </is>
       </c>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="13" t="n"/>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="11" t="n"/>
+      <c r="D49" s="14" t="n"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>Salami</t>
         </is>
       </c>
-      <c r="B49" s="10" t="n"/>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="11" t="n"/>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="B50" s="11" t="n"/>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="12" t="n"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>Salchicha Italiana</t>
         </is>
       </c>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="13" t="n"/>
-    </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="B51" s="11" t="n"/>
+      <c r="C51" s="11" t="n"/>
+      <c r="D51" s="14" t="n"/>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Tocino</t>
         </is>
       </c>
-      <c r="B51" s="10" t="n"/>
-      <c r="C51" s="10" t="n"/>
-      <c r="D51" s="11" t="n"/>
-    </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="12" t="inlineStr"/>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="10" t="n"/>
-      <c r="D52" s="13" t="n"/>
+      <c r="B52" s="11" t="n"/>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="12" t="n"/>
     </row>
     <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="9" t="inlineStr"/>
-      <c r="B53" s="10" t="n"/>
-      <c r="C53" s="10" t="n"/>
-      <c r="D53" s="11" t="n"/>
-    </row>
-    <row r="54" ht="19" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A53" s="13" t="inlineStr"/>
+      <c r="B53" s="11" t="n"/>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="14" t="n"/>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="10" t="inlineStr"/>
+      <c r="B54" s="11" t="n"/>
+      <c r="C54" s="11" t="n"/>
+      <c r="D54" s="12" t="n"/>
+    </row>
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>ALMACÉN</t>
         </is>
       </c>
-      <c r="B54" s="8" t="n"/>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="B55" s="9" t="n"/>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="9" t="n"/>
+    </row>
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>Aceite</t>
         </is>
       </c>
-      <c r="B55" s="10" t="n"/>
-      <c r="C55" s="10" t="n"/>
-      <c r="D55" s="11" t="n"/>
-    </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="B56" s="11" t="n"/>
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="12" t="n"/>
+    </row>
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t>Aceite freidora</t>
         </is>
       </c>
-      <c r="B56" s="10" t="n"/>
-      <c r="C56" s="10" t="n"/>
-      <c r="D56" s="13" t="n"/>
-    </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="B57" s="11" t="n"/>
+      <c r="C57" s="11" t="n"/>
+      <c r="D57" s="14" t="n"/>
+    </row>
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>Aceite de Oliva</t>
         </is>
       </c>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="11" t="n"/>
-    </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="B58" s="11" t="n"/>
+      <c r="C58" s="11" t="n"/>
+      <c r="D58" s="12" t="n"/>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>Aceituna negra</t>
         </is>
       </c>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="13" t="n"/>
-    </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="B59" s="11" t="n"/>
+      <c r="C59" s="11" t="n"/>
+      <c r="D59" s="14" t="n"/>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>Ajo en Polvo</t>
         </is>
       </c>
-      <c r="B59" s="10" t="n"/>
-      <c r="C59" s="10" t="n"/>
-      <c r="D59" s="11" t="n"/>
-    </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="12" t="inlineStr">
+      <c r="B60" s="11" t="n"/>
+      <c r="C60" s="11" t="n"/>
+      <c r="D60" s="12" t="n"/>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>Albahaca Deshidratada</t>
         </is>
       </c>
-      <c r="B60" s="10" t="n"/>
-      <c r="C60" s="10" t="n"/>
-      <c r="D60" s="13" t="n"/>
-    </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="B61" s="11" t="n"/>
+      <c r="C61" s="11" t="n"/>
+      <c r="D61" s="14" t="n"/>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>Alcachofa</t>
         </is>
       </c>
-      <c r="B61" s="10" t="n"/>
-      <c r="C61" s="10" t="n"/>
-      <c r="D61" s="11" t="n"/>
-    </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="B62" s="11" t="n"/>
+      <c r="C62" s="11" t="n"/>
+      <c r="D62" s="12" t="n"/>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>Aluminio</t>
         </is>
       </c>
-      <c r="B62" s="10" t="n"/>
-      <c r="C62" s="10" t="n"/>
-      <c r="D62" s="13" t="n"/>
-    </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="B63" s="11" t="n"/>
+      <c r="C63" s="11" t="n"/>
+      <c r="D63" s="14" t="n"/>
+    </row>
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>Anís Estrella</t>
         </is>
       </c>
-      <c r="B63" s="10" t="n"/>
-      <c r="C63" s="10" t="n"/>
-      <c r="D63" s="11" t="n"/>
-    </row>
-    <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="B64" s="11" t="n"/>
+      <c r="C64" s="11" t="n"/>
+      <c r="D64" s="12" t="n"/>
+    </row>
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>Arándanos</t>
         </is>
       </c>
-      <c r="B64" s="10" t="n"/>
-      <c r="C64" s="10" t="n"/>
-      <c r="D64" s="13" t="n"/>
-    </row>
-    <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="B65" s="11" t="n"/>
+      <c r="C65" s="11" t="n"/>
+      <c r="D65" s="14" t="n"/>
+    </row>
+    <row r="66" ht="17" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>Azúcar</t>
         </is>
       </c>
-      <c r="B65" s="10" t="n"/>
-      <c r="C65" s="10" t="n"/>
-      <c r="D65" s="11" t="n"/>
-    </row>
-    <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="12" t="inlineStr">
+      <c r="B66" s="11" t="n"/>
+      <c r="C66" s="11" t="n"/>
+      <c r="D66" s="12" t="n"/>
+    </row>
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>Bactericida</t>
         </is>
       </c>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="13" t="n"/>
-    </row>
-    <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="B67" s="11" t="n"/>
+      <c r="C67" s="11" t="n"/>
+      <c r="D67" s="14" t="n"/>
+    </row>
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>Cacahuate</t>
         </is>
       </c>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="11" t="n"/>
-    </row>
-    <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="12" t="inlineStr">
+      <c r="B68" s="11" t="n"/>
+      <c r="C68" s="11" t="n"/>
+      <c r="D68" s="12" t="n"/>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="13" t="inlineStr">
         <is>
           <t>Cardamomo</t>
         </is>
       </c>
-      <c r="B68" s="10" t="n"/>
-      <c r="C68" s="10" t="n"/>
-      <c r="D68" s="13" t="n"/>
-    </row>
-    <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="9" t="inlineStr">
+      <c r="B69" s="11" t="n"/>
+      <c r="C69" s="11" t="n"/>
+      <c r="D69" s="14" t="n"/>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>Catsup</t>
         </is>
       </c>
-      <c r="B69" s="10" t="n"/>
-      <c r="C69" s="10" t="n"/>
-      <c r="D69" s="11" t="n"/>
-    </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="12" t="inlineStr">
+      <c r="B70" s="11" t="n"/>
+      <c r="C70" s="11" t="n"/>
+      <c r="D70" s="12" t="n"/>
+    </row>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="13" t="inlineStr">
         <is>
           <t>Cebolla en Polvo</t>
         </is>
       </c>
-      <c r="B70" s="10" t="n"/>
-      <c r="C70" s="10" t="n"/>
-      <c r="D70" s="13" t="n"/>
-    </row>
-    <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="B71" s="11" t="n"/>
+      <c r="C71" s="11" t="n"/>
+      <c r="D71" s="14" t="n"/>
+    </row>
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>Chipotle</t>
         </is>
       </c>
-      <c r="B71" s="10" t="n"/>
-      <c r="C71" s="10" t="n"/>
-      <c r="D71" s="11" t="n"/>
-    </row>
-    <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="12" t="inlineStr">
+      <c r="B72" s="11" t="n"/>
+      <c r="C72" s="11" t="n"/>
+      <c r="D72" s="12" t="n"/>
+    </row>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="13" t="inlineStr">
         <is>
           <t>Chocolate</t>
         </is>
       </c>
-      <c r="B72" s="10" t="n"/>
-      <c r="C72" s="10" t="n"/>
-      <c r="D72" s="13" t="n"/>
-    </row>
-    <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="9" t="inlineStr">
+      <c r="B73" s="11" t="n"/>
+      <c r="C73" s="11" t="n"/>
+      <c r="D73" s="14" t="n"/>
+    </row>
+    <row r="74" ht="17" customHeight="1">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>Clavo</t>
         </is>
       </c>
-      <c r="B73" s="10" t="n"/>
-      <c r="C73" s="10" t="n"/>
-      <c r="D73" s="11" t="n"/>
-    </row>
-    <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="12" t="inlineStr">
+      <c r="B74" s="11" t="n"/>
+      <c r="C74" s="11" t="n"/>
+      <c r="D74" s="12" t="n"/>
+    </row>
+    <row r="75" ht="17" customHeight="1">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>Condimento Italiano</t>
         </is>
       </c>
-      <c r="B74" s="10" t="n"/>
-      <c r="C74" s="10" t="n"/>
-      <c r="D74" s="13" t="n"/>
-    </row>
-    <row r="75" ht="17" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="B75" s="11" t="n"/>
+      <c r="C75" s="11" t="n"/>
+      <c r="D75" s="14" t="n"/>
+    </row>
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>Consomé</t>
         </is>
       </c>
-      <c r="B75" s="10" t="n"/>
-      <c r="C75" s="10" t="n"/>
-      <c r="D75" s="11" t="n"/>
-    </row>
-    <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="12" t="inlineStr">
+      <c r="B76" s="11" t="n"/>
+      <c r="C76" s="11" t="n"/>
+      <c r="D76" s="12" t="n"/>
+    </row>
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="13" t="inlineStr">
         <is>
           <t>Crema para Batir</t>
         </is>
       </c>
-      <c r="B76" s="10" t="n"/>
-      <c r="C76" s="10" t="n"/>
-      <c r="D76" s="13" t="n"/>
-    </row>
-    <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="9" t="inlineStr">
+      <c r="B77" s="11" t="n"/>
+      <c r="C77" s="11" t="n"/>
+      <c r="D77" s="14" t="n"/>
+    </row>
+    <row r="78" ht="17" customHeight="1">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>Espagueti</t>
         </is>
       </c>
-      <c r="B77" s="10" t="n"/>
-      <c r="C77" s="10" t="n"/>
-      <c r="D77" s="11" t="n"/>
-    </row>
-    <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="12" t="inlineStr">
+      <c r="B78" s="11" t="n"/>
+      <c r="C78" s="11" t="n"/>
+      <c r="D78" s="12" t="n"/>
+    </row>
+    <row r="79" ht="17" customHeight="1">
+      <c r="A79" s="13" t="inlineStr">
         <is>
           <t>Frutos rojos</t>
         </is>
       </c>
-      <c r="B78" s="10" t="n"/>
-      <c r="C78" s="10" t="n"/>
-      <c r="D78" s="13" t="n"/>
-    </row>
-    <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="9" t="inlineStr">
+      <c r="B79" s="11" t="n"/>
+      <c r="C79" s="11" t="n"/>
+      <c r="D79" s="14" t="n"/>
+    </row>
+    <row r="80" ht="17" customHeight="1">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>Grenetina</t>
         </is>
       </c>
-      <c r="B79" s="10" t="n"/>
-      <c r="C79" s="10" t="n"/>
-      <c r="D79" s="11" t="n"/>
-    </row>
-    <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="12" t="inlineStr">
+      <c r="B80" s="11" t="n"/>
+      <c r="C80" s="11" t="n"/>
+      <c r="D80" s="12" t="n"/>
+    </row>
+    <row r="81" ht="17" customHeight="1">
+      <c r="A81" s="13" t="inlineStr">
         <is>
           <t>Harina</t>
         </is>
       </c>
-      <c r="B80" s="10" t="n"/>
-      <c r="C80" s="10" t="n"/>
-      <c r="D80" s="13" t="n"/>
-    </row>
-    <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="9" t="inlineStr">
+      <c r="B81" s="11" t="n"/>
+      <c r="C81" s="11" t="n"/>
+      <c r="D81" s="14" t="n"/>
+    </row>
+    <row r="82" ht="17" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>Harina de arroz</t>
         </is>
       </c>
-      <c r="B81" s="10" t="n"/>
-      <c r="C81" s="10" t="n"/>
-      <c r="D81" s="11" t="n"/>
-    </row>
-    <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="12" t="inlineStr">
+      <c r="B82" s="11" t="n"/>
+      <c r="C82" s="11" t="n"/>
+      <c r="D82" s="12" t="n"/>
+    </row>
+    <row r="83" ht="17" customHeight="1">
+      <c r="A83" s="13" t="inlineStr">
         <is>
           <t>Hojaldra</t>
         </is>
       </c>
-      <c r="B82" s="10" t="n"/>
-      <c r="C82" s="10" t="n"/>
-      <c r="D82" s="13" t="n"/>
-    </row>
-    <row r="83" ht="17" customHeight="1">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="B83" s="11" t="n"/>
+      <c r="C83" s="11" t="n"/>
+      <c r="D83" s="14" t="n"/>
+    </row>
+    <row r="84" ht="17" customHeight="1">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>Jamón Serrano</t>
         </is>
       </c>
-      <c r="B83" s="10" t="n"/>
-      <c r="C83" s="10" t="n"/>
-      <c r="D83" s="11" t="n"/>
-    </row>
-    <row r="84" ht="17" customHeight="1">
-      <c r="A84" s="12" t="inlineStr">
+      <c r="B84" s="11" t="n"/>
+      <c r="C84" s="11" t="n"/>
+      <c r="D84" s="12" t="n"/>
+    </row>
+    <row r="85" ht="17" customHeight="1">
+      <c r="A85" s="13" t="inlineStr">
         <is>
           <t>Leche evaporada</t>
         </is>
       </c>
-      <c r="B84" s="10" t="n"/>
-      <c r="C84" s="10" t="n"/>
-      <c r="D84" s="13" t="n"/>
-    </row>
-    <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="9" t="inlineStr">
+      <c r="B85" s="11" t="n"/>
+      <c r="C85" s="11" t="n"/>
+      <c r="D85" s="14" t="n"/>
+    </row>
+    <row r="86" ht="17" customHeight="1">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>Leche Entera</t>
         </is>
       </c>
-      <c r="B85" s="10" t="n"/>
-      <c r="C85" s="10" t="n"/>
-      <c r="D85" s="11" t="n"/>
-    </row>
-    <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="12" t="inlineStr">
+      <c r="B86" s="11" t="n"/>
+      <c r="C86" s="11" t="n"/>
+      <c r="D86" s="12" t="n"/>
+    </row>
+    <row r="87" ht="17" customHeight="1">
+      <c r="A87" s="13" t="inlineStr">
         <is>
           <t>Lemon Pepper</t>
         </is>
       </c>
-      <c r="B86" s="10" t="n"/>
-      <c r="C86" s="10" t="n"/>
-      <c r="D86" s="13" t="n"/>
-    </row>
-    <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="9" t="inlineStr">
+      <c r="B87" s="11" t="n"/>
+      <c r="C87" s="11" t="n"/>
+      <c r="D87" s="14" t="n"/>
+    </row>
+    <row r="88" ht="17" customHeight="1">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>Levadura</t>
         </is>
       </c>
-      <c r="B87" s="10" t="n"/>
-      <c r="C87" s="10" t="n"/>
-      <c r="D87" s="11" t="n"/>
-    </row>
-    <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="12" t="inlineStr">
+      <c r="B88" s="11" t="n"/>
+      <c r="C88" s="11" t="n"/>
+      <c r="D88" s="12" t="n"/>
+    </row>
+    <row r="89" ht="17" customHeight="1">
+      <c r="A89" s="13" t="inlineStr">
         <is>
           <t>Maizena</t>
         </is>
       </c>
-      <c r="B88" s="10" t="n"/>
-      <c r="C88" s="10" t="n"/>
-      <c r="D88" s="13" t="n"/>
-    </row>
-    <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="9" t="inlineStr">
+      <c r="B89" s="11" t="n"/>
+      <c r="C89" s="11" t="n"/>
+      <c r="D89" s="14" t="n"/>
+    </row>
+    <row r="90" ht="17" customHeight="1">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>Margarina</t>
         </is>
       </c>
-      <c r="B89" s="10" t="n"/>
-      <c r="C89" s="10" t="n"/>
-      <c r="D89" s="11" t="n"/>
-    </row>
-    <row r="90" ht="17" customHeight="1">
-      <c r="A90" s="12" t="inlineStr">
+      <c r="B90" s="11" t="n"/>
+      <c r="C90" s="11" t="n"/>
+      <c r="D90" s="12" t="n"/>
+    </row>
+    <row r="91" ht="17" customHeight="1">
+      <c r="A91" s="13" t="inlineStr">
         <is>
           <t>Mayonesa</t>
         </is>
       </c>
-      <c r="B90" s="10" t="n"/>
-      <c r="C90" s="10" t="n"/>
-      <c r="D90" s="13" t="n"/>
-    </row>
-    <row r="91" ht="17" customHeight="1">
-      <c r="A91" s="9" t="inlineStr">
+      <c r="B91" s="11" t="n"/>
+      <c r="C91" s="11" t="n"/>
+      <c r="D91" s="14" t="n"/>
+    </row>
+    <row r="92" ht="17" customHeight="1">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>Media crema</t>
         </is>
       </c>
-      <c r="B91" s="10" t="n"/>
-      <c r="C91" s="10" t="n"/>
-      <c r="D91" s="11" t="n"/>
-    </row>
-    <row r="92" ht="17" customHeight="1">
-      <c r="A92" s="12" t="inlineStr">
+      <c r="B92" s="11" t="n"/>
+      <c r="C92" s="11" t="n"/>
+      <c r="D92" s="12" t="n"/>
+    </row>
+    <row r="93" ht="17" customHeight="1">
+      <c r="A93" s="13" t="inlineStr">
         <is>
           <t>Miel</t>
         </is>
       </c>
-      <c r="B92" s="10" t="n"/>
-      <c r="C92" s="10" t="n"/>
-      <c r="D92" s="13" t="n"/>
-    </row>
-    <row r="93" ht="17" customHeight="1">
-      <c r="A93" s="9" t="inlineStr">
+      <c r="B93" s="11" t="n"/>
+      <c r="C93" s="11" t="n"/>
+      <c r="D93" s="14" t="n"/>
+    </row>
+    <row r="94" ht="17" customHeight="1">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>Mostaza</t>
         </is>
       </c>
-      <c r="B93" s="10" t="n"/>
-      <c r="C93" s="10" t="n"/>
-      <c r="D93" s="11" t="n"/>
-    </row>
-    <row r="94" ht="17" customHeight="1">
-      <c r="A94" s="12" t="inlineStr">
+      <c r="B94" s="11" t="n"/>
+      <c r="C94" s="11" t="n"/>
+      <c r="D94" s="12" t="n"/>
+    </row>
+    <row r="95" ht="17" customHeight="1">
+      <c r="A95" s="13" t="inlineStr">
         <is>
           <t>Nuez Caramelizada</t>
         </is>
       </c>
-      <c r="B94" s="10" t="n"/>
-      <c r="C94" s="10" t="n"/>
-      <c r="D94" s="13" t="n"/>
-    </row>
-    <row r="95" ht="17" customHeight="1">
-      <c r="A95" s="9" t="inlineStr">
+      <c r="B95" s="11" t="n"/>
+      <c r="C95" s="11" t="n"/>
+      <c r="D95" s="14" t="n"/>
+    </row>
+    <row r="96" ht="17" customHeight="1">
+      <c r="A96" s="10" t="inlineStr">
         <is>
           <t>Ostiones</t>
         </is>
       </c>
-      <c r="B95" s="10" t="n"/>
-      <c r="C95" s="10" t="n"/>
-      <c r="D95" s="11" t="n"/>
-    </row>
-    <row r="96" ht="17" customHeight="1">
-      <c r="A96" s="12" t="inlineStr">
+      <c r="B96" s="11" t="n"/>
+      <c r="C96" s="11" t="n"/>
+      <c r="D96" s="12" t="n"/>
+    </row>
+    <row r="97" ht="17" customHeight="1">
+      <c r="A97" s="13" t="inlineStr">
         <is>
           <t>Paprika</t>
         </is>
       </c>
-      <c r="B96" s="10" t="n"/>
-      <c r="C96" s="10" t="n"/>
-      <c r="D96" s="13" t="n"/>
-    </row>
-    <row r="97" ht="17" customHeight="1">
-      <c r="A97" s="9" t="inlineStr">
+      <c r="B97" s="11" t="n"/>
+      <c r="C97" s="11" t="n"/>
+      <c r="D97" s="14" t="n"/>
+    </row>
+    <row r="98" ht="17" customHeight="1">
+      <c r="A98" s="10" t="inlineStr">
         <is>
           <t>Pimienta trozada</t>
         </is>
       </c>
-      <c r="B97" s="10" t="n"/>
-      <c r="C97" s="10" t="n"/>
-      <c r="D97" s="11" t="n"/>
-    </row>
-    <row r="98" ht="17" customHeight="1">
-      <c r="A98" s="12" t="inlineStr">
+      <c r="B98" s="11" t="n"/>
+      <c r="C98" s="11" t="n"/>
+      <c r="D98" s="12" t="n"/>
+    </row>
+    <row r="99" ht="17" customHeight="1">
+      <c r="A99" s="13" t="inlineStr">
         <is>
           <t>Pimiento Morrón</t>
         </is>
       </c>
-      <c r="B98" s="10" t="n"/>
-      <c r="C98" s="10" t="n"/>
-      <c r="D98" s="13" t="n"/>
-    </row>
-    <row r="99" ht="17" customHeight="1">
-      <c r="A99" s="9" t="inlineStr">
+      <c r="B99" s="11" t="n"/>
+      <c r="C99" s="11" t="n"/>
+      <c r="D99" s="14" t="n"/>
+    </row>
+    <row r="100" ht="17" customHeight="1">
+      <c r="A100" s="10" t="inlineStr">
         <is>
           <t>Piña</t>
         </is>
       </c>
-      <c r="B99" s="10" t="n"/>
-      <c r="C99" s="10" t="n"/>
-      <c r="D99" s="11" t="n"/>
-    </row>
-    <row r="100" ht="17" customHeight="1">
-      <c r="A100" s="12" t="inlineStr">
+      <c r="B100" s="11" t="n"/>
+      <c r="C100" s="11" t="n"/>
+      <c r="D100" s="12" t="n"/>
+    </row>
+    <row r="101" ht="17" customHeight="1">
+      <c r="A101" s="13" t="inlineStr">
         <is>
           <t>Queso Amarillo</t>
         </is>
       </c>
-      <c r="B100" s="10" t="n"/>
-      <c r="C100" s="10" t="n"/>
-      <c r="D100" s="13" t="n"/>
-    </row>
-    <row r="101" ht="17" customHeight="1">
-      <c r="A101" s="9" t="inlineStr">
+      <c r="B101" s="11" t="n"/>
+      <c r="C101" s="11" t="n"/>
+      <c r="D101" s="14" t="n"/>
+    </row>
+    <row r="102" ht="17" customHeight="1">
+      <c r="A102" s="10" t="inlineStr">
         <is>
           <t>Queso Cabra</t>
         </is>
       </c>
-      <c r="B101" s="10" t="n"/>
-      <c r="C101" s="10" t="n"/>
-      <c r="D101" s="11" t="n"/>
-    </row>
-    <row r="102" ht="17" customHeight="1">
-      <c r="A102" s="12" t="inlineStr">
+      <c r="B102" s="11" t="n"/>
+      <c r="C102" s="11" t="n"/>
+      <c r="D102" s="12" t="n"/>
+    </row>
+    <row r="103" ht="17" customHeight="1">
+      <c r="A103" s="13" t="inlineStr">
         <is>
           <t>Queso Crema</t>
         </is>
       </c>
-      <c r="B102" s="10" t="n"/>
-      <c r="C102" s="10" t="n"/>
-      <c r="D102" s="13" t="n"/>
-    </row>
-    <row r="103" ht="17" customHeight="1">
-      <c r="A103" s="9" t="inlineStr">
+      <c r="B103" s="11" t="n"/>
+      <c r="C103" s="11" t="n"/>
+      <c r="D103" s="14" t="n"/>
+    </row>
+    <row r="104" ht="17" customHeight="1">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>Queso Mozzarella</t>
         </is>
       </c>
-      <c r="B103" s="10" t="n"/>
-      <c r="C103" s="10" t="n"/>
-      <c r="D103" s="11" t="n"/>
-    </row>
-    <row r="104" ht="17" customHeight="1">
-      <c r="A104" s="12" t="inlineStr">
+      <c r="B104" s="11" t="n"/>
+      <c r="C104" s="11" t="n"/>
+      <c r="D104" s="12" t="n"/>
+    </row>
+    <row r="105" ht="17" customHeight="1">
+      <c r="A105" s="13" t="inlineStr">
         <is>
           <t>Queso Panela</t>
         </is>
       </c>
-      <c r="B104" s="10" t="n"/>
-      <c r="C104" s="10" t="n"/>
-      <c r="D104" s="13" t="n"/>
-    </row>
-    <row r="105" ht="17" customHeight="1">
-      <c r="A105" s="9" t="inlineStr">
+      <c r="B105" s="11" t="n"/>
+      <c r="C105" s="11" t="n"/>
+      <c r="D105" s="14" t="n"/>
+    </row>
+    <row r="106" ht="17" customHeight="1">
+      <c r="A106" s="10" t="inlineStr">
         <is>
           <t>Queso Parmesano</t>
         </is>
       </c>
-      <c r="B105" s="10" t="n"/>
-      <c r="C105" s="10" t="n"/>
-      <c r="D105" s="11" t="n"/>
-    </row>
-    <row r="106" ht="17" customHeight="1">
-      <c r="A106" s="12" t="inlineStr">
+      <c r="B106" s="11" t="n"/>
+      <c r="C106" s="11" t="n"/>
+      <c r="D106" s="12" t="n"/>
+    </row>
+    <row r="107" ht="17" customHeight="1">
+      <c r="A107" s="13" t="inlineStr">
         <is>
           <t>Queso para Pastas</t>
         </is>
       </c>
-      <c r="B106" s="10" t="n"/>
-      <c r="C106" s="10" t="n"/>
-      <c r="D106" s="13" t="n"/>
-    </row>
-    <row r="107" ht="17" customHeight="1">
-      <c r="A107" s="9" t="inlineStr">
+      <c r="B107" s="11" t="n"/>
+      <c r="C107" s="11" t="n"/>
+      <c r="D107" s="14" t="n"/>
+    </row>
+    <row r="108" ht="17" customHeight="1">
+      <c r="A108" s="10" t="inlineStr">
         <is>
           <t>Sal</t>
         </is>
       </c>
-      <c r="B107" s="10" t="n"/>
-      <c r="C107" s="10" t="n"/>
-      <c r="D107" s="11" t="n"/>
-    </row>
-    <row r="108" ht="17" customHeight="1">
-      <c r="A108" s="12" t="inlineStr">
+      <c r="B108" s="11" t="n"/>
+      <c r="C108" s="11" t="n"/>
+      <c r="D108" s="12" t="n"/>
+    </row>
+    <row r="109" ht="17" customHeight="1">
+      <c r="A109" s="13" t="inlineStr">
         <is>
           <t>Sal de Mar</t>
         </is>
       </c>
-      <c r="B108" s="10" t="n"/>
-      <c r="C108" s="10" t="n"/>
-      <c r="D108" s="13" t="n"/>
-    </row>
-    <row r="109" ht="17" customHeight="1">
-      <c r="A109" s="9" t="inlineStr">
+      <c r="B109" s="11" t="n"/>
+      <c r="C109" s="11" t="n"/>
+      <c r="D109" s="14" t="n"/>
+    </row>
+    <row r="110" ht="17" customHeight="1">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>Salsa Sriracha</t>
         </is>
       </c>
-      <c r="B109" s="10" t="n"/>
-      <c r="C109" s="10" t="n"/>
-      <c r="D109" s="11" t="n"/>
-    </row>
-    <row r="110" ht="17" customHeight="1">
-      <c r="A110" s="12" t="inlineStr">
+      <c r="B110" s="11" t="n"/>
+      <c r="C110" s="11" t="n"/>
+      <c r="D110" s="12" t="n"/>
+    </row>
+    <row r="111" ht="17" customHeight="1">
+      <c r="A111" s="13" t="inlineStr">
         <is>
           <t>Tomate pelado</t>
         </is>
       </c>
-      <c r="B110" s="10" t="n"/>
-      <c r="C110" s="10" t="n"/>
-      <c r="D110" s="13" t="n"/>
-    </row>
-    <row r="111" ht="17" customHeight="1">
-      <c r="A111" s="9" t="inlineStr">
+      <c r="B111" s="11" t="n"/>
+      <c r="C111" s="11" t="n"/>
+      <c r="D111" s="14" t="n"/>
+    </row>
+    <row r="112" ht="17" customHeight="1">
+      <c r="A112" s="10" t="inlineStr">
         <is>
           <t>Tomate Deshidratado</t>
         </is>
       </c>
-      <c r="B111" s="10" t="n"/>
-      <c r="C111" s="10" t="n"/>
-      <c r="D111" s="11" t="n"/>
-    </row>
-    <row r="112" ht="17" customHeight="1">
-      <c r="A112" s="12" t="inlineStr">
+      <c r="B112" s="11" t="n"/>
+      <c r="C112" s="11" t="n"/>
+      <c r="D112" s="12" t="n"/>
+    </row>
+    <row r="113" ht="17" customHeight="1">
+      <c r="A113" s="13" t="inlineStr">
         <is>
           <t>Vainilla</t>
         </is>
       </c>
-      <c r="B112" s="10" t="n"/>
-      <c r="C112" s="10" t="n"/>
-      <c r="D112" s="13" t="n"/>
-    </row>
-    <row r="113" ht="17" customHeight="1">
-      <c r="A113" s="9" t="inlineStr">
+      <c r="B113" s="11" t="n"/>
+      <c r="C113" s="11" t="n"/>
+      <c r="D113" s="14" t="n"/>
+    </row>
+    <row r="114" ht="17" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>Vinagre Balsámico</t>
         </is>
       </c>
-      <c r="B113" s="10" t="n"/>
-      <c r="C113" s="10" t="n"/>
-      <c r="D113" s="11" t="n"/>
-    </row>
-    <row r="114" ht="17" customHeight="1">
-      <c r="A114" s="12" t="inlineStr">
+      <c r="B114" s="11" t="n"/>
+      <c r="C114" s="11" t="n"/>
+      <c r="D114" s="12" t="n"/>
+    </row>
+    <row r="115" ht="17" customHeight="1">
+      <c r="A115" s="13" t="inlineStr">
         <is>
           <t>Vinagre Blanco</t>
         </is>
       </c>
-      <c r="B114" s="10" t="n"/>
-      <c r="C114" s="10" t="n"/>
-      <c r="D114" s="13" t="n"/>
-    </row>
-    <row r="115" ht="17" customHeight="1">
-      <c r="A115" s="9" t="inlineStr">
+      <c r="B115" s="11" t="n"/>
+      <c r="C115" s="11" t="n"/>
+      <c r="D115" s="14" t="n"/>
+    </row>
+    <row r="116" ht="17" customHeight="1">
+      <c r="A116" s="10" t="inlineStr">
         <is>
           <t>Vino Blanco</t>
         </is>
       </c>
-      <c r="B115" s="10" t="n"/>
-      <c r="C115" s="10" t="n"/>
-      <c r="D115" s="11" t="n"/>
-    </row>
-    <row r="116" ht="17" customHeight="1">
-      <c r="A116" s="12" t="inlineStr">
+      <c r="B116" s="11" t="n"/>
+      <c r="C116" s="11" t="n"/>
+      <c r="D116" s="12" t="n"/>
+    </row>
+    <row r="117" ht="17" customHeight="1">
+      <c r="A117" s="13" t="inlineStr">
         <is>
           <t>Vino Tinto</t>
         </is>
       </c>
-      <c r="B116" s="10" t="n"/>
-      <c r="C116" s="10" t="n"/>
-      <c r="D116" s="13" t="n"/>
-    </row>
-    <row r="117" ht="17" customHeight="1">
-      <c r="A117" s="9" t="inlineStr">
+      <c r="B117" s="11" t="n"/>
+      <c r="C117" s="11" t="n"/>
+      <c r="D117" s="14" t="n"/>
+    </row>
+    <row r="118" ht="17" customHeight="1">
+      <c r="A118" s="10" t="inlineStr">
         <is>
           <t>Vitafil</t>
         </is>
       </c>
-      <c r="B117" s="10" t="n"/>
-      <c r="C117" s="10" t="n"/>
-      <c r="D117" s="11" t="n"/>
-    </row>
-    <row r="118" ht="17" customHeight="1">
-      <c r="A118" s="12" t="inlineStr">
+      <c r="B118" s="11" t="n"/>
+      <c r="C118" s="11" t="n"/>
+      <c r="D118" s="12" t="n"/>
+    </row>
+    <row r="119" ht="17" customHeight="1">
+      <c r="A119" s="13" t="inlineStr">
         <is>
           <t>Yogurt Natural</t>
         </is>
       </c>
-      <c r="B118" s="10" t="n"/>
-      <c r="C118" s="10" t="n"/>
-      <c r="D118" s="13" t="n"/>
-    </row>
-    <row r="119" ht="17" customHeight="1">
-      <c r="A119" s="9" t="inlineStr"/>
-      <c r="B119" s="10" t="n"/>
-      <c r="C119" s="10" t="n"/>
-      <c r="D119" s="11" t="n"/>
+      <c r="B119" s="11" t="n"/>
+      <c r="C119" s="11" t="n"/>
+      <c r="D119" s="14" t="n"/>
     </row>
     <row r="120" ht="17" customHeight="1">
-      <c r="A120" s="12" t="inlineStr"/>
-      <c r="B120" s="10" t="n"/>
-      <c r="C120" s="10" t="n"/>
-      <c r="D120" s="13" t="n"/>
-    </row>
-    <row r="121" ht="19" customHeight="1">
-      <c r="A121" s="7" t="inlineStr">
+      <c r="A120" s="10" t="inlineStr"/>
+      <c r="B120" s="11" t="n"/>
+      <c r="C120" s="11" t="n"/>
+      <c r="D120" s="12" t="n"/>
+    </row>
+    <row r="121" ht="17" customHeight="1">
+      <c r="A121" s="13" t="inlineStr"/>
+      <c r="B121" s="11" t="n"/>
+      <c r="C121" s="11" t="n"/>
+      <c r="D121" s="14" t="n"/>
+    </row>
+    <row r="122" ht="19" customHeight="1">
+      <c r="A122" s="8" t="inlineStr">
         <is>
           <t>LIMPIEZA</t>
         </is>
       </c>
-      <c r="B121" s="8" t="n"/>
-      <c r="C121" s="8" t="n"/>
-      <c r="D121" s="8" t="n"/>
-    </row>
-    <row r="122" ht="17" customHeight="1">
-      <c r="A122" s="9" t="inlineStr">
+      <c r="B122" s="9" t="n"/>
+      <c r="C122" s="9" t="n"/>
+      <c r="D122" s="9" t="n"/>
+    </row>
+    <row r="123" ht="17" customHeight="1">
+      <c r="A123" s="10" t="inlineStr">
         <is>
           <t>Bolsa camiseta</t>
         </is>
       </c>
-      <c r="B122" s="10" t="n"/>
-      <c r="C122" s="10" t="n"/>
-      <c r="D122" s="11" t="n"/>
-    </row>
-    <row r="123" ht="17" customHeight="1">
-      <c r="A123" s="12" t="inlineStr">
+      <c r="B123" s="11" t="n"/>
+      <c r="C123" s="11" t="n"/>
+      <c r="D123" s="12" t="n"/>
+    </row>
+    <row r="124" ht="17" customHeight="1">
+      <c r="A124" s="13" t="inlineStr">
         <is>
           <t>Bolsas 1/2 k</t>
         </is>
       </c>
-      <c r="B123" s="10" t="n"/>
-      <c r="C123" s="10" t="n"/>
-      <c r="D123" s="13" t="n"/>
-    </row>
-    <row r="124" ht="17" customHeight="1">
-      <c r="A124" s="9" t="inlineStr">
+      <c r="B124" s="11" t="n"/>
+      <c r="C124" s="11" t="n"/>
+      <c r="D124" s="14" t="n"/>
+    </row>
+    <row r="125" ht="17" customHeight="1">
+      <c r="A125" s="10" t="inlineStr">
         <is>
           <t>Bolsas 1 k</t>
         </is>
       </c>
-      <c r="B124" s="10" t="n"/>
-      <c r="C124" s="10" t="n"/>
-      <c r="D124" s="11" t="n"/>
-    </row>
-    <row r="125" ht="17" customHeight="1">
-      <c r="A125" s="12" t="inlineStr">
+      <c r="B125" s="11" t="n"/>
+      <c r="C125" s="11" t="n"/>
+      <c r="D125" s="12" t="n"/>
+    </row>
+    <row r="126" ht="17" customHeight="1">
+      <c r="A126" s="13" t="inlineStr">
         <is>
           <t>Bolsas 3 k</t>
         </is>
       </c>
-      <c r="B125" s="10" t="n"/>
-      <c r="C125" s="10" t="n"/>
-      <c r="D125" s="13" t="n"/>
-    </row>
-    <row r="126" ht="17" customHeight="1">
-      <c r="A126" s="9" t="inlineStr">
+      <c r="B126" s="11" t="n"/>
+      <c r="C126" s="11" t="n"/>
+      <c r="D126" s="14" t="n"/>
+    </row>
+    <row r="127" ht="17" customHeight="1">
+      <c r="A127" s="10" t="inlineStr">
         <is>
           <t>Bolsas de basura N.</t>
         </is>
       </c>
-      <c r="B126" s="10" t="n"/>
-      <c r="C126" s="10" t="n"/>
-      <c r="D126" s="11" t="n"/>
-    </row>
-    <row r="127" ht="17" customHeight="1">
-      <c r="A127" s="12" t="inlineStr">
+      <c r="B127" s="11" t="n"/>
+      <c r="C127" s="11" t="n"/>
+      <c r="D127" s="12" t="n"/>
+    </row>
+    <row r="128" ht="17" customHeight="1">
+      <c r="A128" s="13" t="inlineStr">
         <is>
           <t>Caja pizza 16</t>
         </is>
       </c>
-      <c r="B127" s="10" t="n"/>
-      <c r="C127" s="10" t="n"/>
-      <c r="D127" s="13" t="n"/>
-    </row>
-    <row r="128" ht="17" customHeight="1">
-      <c r="A128" s="9" t="inlineStr">
+      <c r="B128" s="11" t="n"/>
+      <c r="C128" s="11" t="n"/>
+      <c r="D128" s="14" t="n"/>
+    </row>
+    <row r="129" ht="17" customHeight="1">
+      <c r="A129" s="10" t="inlineStr">
         <is>
           <t>Caja pizza 12</t>
         </is>
       </c>
-      <c r="B128" s="10" t="n"/>
-      <c r="C128" s="10" t="n"/>
-      <c r="D128" s="11" t="n"/>
-    </row>
-    <row r="129" ht="17" customHeight="1">
-      <c r="A129" s="12" t="inlineStr">
+      <c r="B129" s="11" t="n"/>
+      <c r="C129" s="11" t="n"/>
+      <c r="D129" s="12" t="n"/>
+    </row>
+    <row r="130" ht="17" customHeight="1">
+      <c r="A130" s="13" t="inlineStr">
         <is>
           <t>Cloro</t>
         </is>
       </c>
-      <c r="B129" s="10" t="n"/>
-      <c r="C129" s="10" t="n"/>
-      <c r="D129" s="13" t="n"/>
-    </row>
-    <row r="130" ht="17" customHeight="1">
-      <c r="A130" s="9" t="inlineStr">
+      <c r="B130" s="11" t="n"/>
+      <c r="C130" s="11" t="n"/>
+      <c r="D130" s="14" t="n"/>
+    </row>
+    <row r="131" ht="17" customHeight="1">
+      <c r="A131" s="10" t="inlineStr">
         <is>
           <t>Desengrasante</t>
         </is>
       </c>
-      <c r="B130" s="10" t="n"/>
-      <c r="C130" s="10" t="n"/>
-      <c r="D130" s="11" t="n"/>
-    </row>
-    <row r="131" ht="17" customHeight="1">
-      <c r="A131" s="12" t="inlineStr">
+      <c r="B131" s="11" t="n"/>
+      <c r="C131" s="11" t="n"/>
+      <c r="D131" s="12" t="n"/>
+    </row>
+    <row r="132" ht="17" customHeight="1">
+      <c r="A132" s="13" t="inlineStr">
         <is>
           <t>Escoba</t>
         </is>
       </c>
-      <c r="B131" s="10" t="n"/>
-      <c r="C131" s="10" t="n"/>
-      <c r="D131" s="13" t="n"/>
-    </row>
-    <row r="132" ht="17" customHeight="1">
-      <c r="A132" s="9" t="inlineStr">
+      <c r="B132" s="11" t="n"/>
+      <c r="C132" s="11" t="n"/>
+      <c r="D132" s="14" t="n"/>
+    </row>
+    <row r="133" ht="17" customHeight="1">
+      <c r="A133" s="10" t="inlineStr">
         <is>
           <t>Fabuloso</t>
         </is>
       </c>
-      <c r="B132" s="10" t="n"/>
-      <c r="C132" s="10" t="n"/>
-      <c r="D132" s="11" t="n"/>
-    </row>
-    <row r="133" ht="17" customHeight="1">
-      <c r="A133" s="12" t="inlineStr">
+      <c r="B133" s="11" t="n"/>
+      <c r="C133" s="11" t="n"/>
+      <c r="D133" s="12" t="n"/>
+    </row>
+    <row r="134" ht="17" customHeight="1">
+      <c r="A134" s="13" t="inlineStr">
         <is>
           <t>Fibras Esponja</t>
         </is>
       </c>
-      <c r="B133" s="10" t="n"/>
-      <c r="C133" s="10" t="n"/>
-      <c r="D133" s="13" t="n"/>
-    </row>
-    <row r="134" ht="17" customHeight="1">
-      <c r="A134" s="9" t="inlineStr">
+      <c r="B134" s="11" t="n"/>
+      <c r="C134" s="11" t="n"/>
+      <c r="D134" s="14" t="n"/>
+    </row>
+    <row r="135" ht="17" customHeight="1">
+      <c r="A135" s="10" t="inlineStr">
         <is>
           <t>Fibras Metal</t>
         </is>
       </c>
-      <c r="B134" s="10" t="n"/>
-      <c r="C134" s="10" t="n"/>
-      <c r="D134" s="11" t="n"/>
-    </row>
-    <row r="135" ht="17" customHeight="1">
-      <c r="A135" s="12" t="inlineStr">
+      <c r="B135" s="11" t="n"/>
+      <c r="C135" s="11" t="n"/>
+      <c r="D135" s="12" t="n"/>
+    </row>
+    <row r="136" ht="17" customHeight="1">
+      <c r="A136" s="13" t="inlineStr">
         <is>
           <t>Franela</t>
         </is>
       </c>
-      <c r="B135" s="10" t="n"/>
-      <c r="C135" s="10" t="n"/>
-      <c r="D135" s="13" t="n"/>
-    </row>
-    <row r="136" ht="17" customHeight="1">
-      <c r="A136" s="9" t="inlineStr">
+      <c r="B136" s="11" t="n"/>
+      <c r="C136" s="11" t="n"/>
+      <c r="D136" s="14" t="n"/>
+    </row>
+    <row r="137" ht="17" customHeight="1">
+      <c r="A137" s="10" t="inlineStr">
         <is>
           <t>Jabón para Trastes</t>
         </is>
       </c>
-      <c r="B136" s="10" t="n"/>
-      <c r="C136" s="10" t="n"/>
-      <c r="D136" s="11" t="n"/>
-    </row>
-    <row r="137" ht="17" customHeight="1">
-      <c r="A137" s="12" t="inlineStr">
+      <c r="B137" s="11" t="n"/>
+      <c r="C137" s="11" t="n"/>
+      <c r="D137" s="12" t="n"/>
+    </row>
+    <row r="138" ht="17" customHeight="1">
+      <c r="A138" s="13" t="inlineStr">
         <is>
           <t>Recogedor</t>
         </is>
       </c>
-      <c r="B137" s="10" t="n"/>
-      <c r="C137" s="10" t="n"/>
-      <c r="D137" s="13" t="n"/>
-    </row>
-    <row r="138" ht="17" customHeight="1">
-      <c r="A138" s="9" t="inlineStr">
+      <c r="B138" s="11" t="n"/>
+      <c r="C138" s="11" t="n"/>
+      <c r="D138" s="14" t="n"/>
+    </row>
+    <row r="139" ht="17" customHeight="1">
+      <c r="A139" s="10" t="inlineStr">
         <is>
           <t>Trapeador</t>
         </is>
       </c>
-      <c r="B138" s="10" t="n"/>
-      <c r="C138" s="10" t="n"/>
-      <c r="D138" s="11" t="n"/>
-    </row>
-    <row r="139" ht="17" customHeight="1">
-      <c r="A139" s="12" t="inlineStr"/>
-      <c r="B139" s="10" t="n"/>
-      <c r="C139" s="10" t="n"/>
-      <c r="D139" s="13" t="n"/>
+      <c r="B139" s="11" t="n"/>
+      <c r="C139" s="11" t="n"/>
+      <c r="D139" s="12" t="n"/>
     </row>
     <row r="140" ht="17" customHeight="1">
-      <c r="A140" s="9" t="inlineStr"/>
-      <c r="B140" s="10" t="n"/>
-      <c r="C140" s="10" t="n"/>
-      <c r="D140" s="11" t="n"/>
+      <c r="A140" s="13" t="inlineStr"/>
+      <c r="B140" s="11" t="n"/>
+      <c r="C140" s="11" t="n"/>
+      <c r="D140" s="14" t="n"/>
+    </row>
+    <row r="141" ht="17" customHeight="1">
+      <c r="A141" s="10" t="inlineStr"/>
+      <c r="B141" s="11" t="n"/>
+      <c r="C141" s="11" t="n"/>
+      <c r="D141" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A122:D122"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A55:D55"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A121:D121"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/CHICAGO DEEP DISH PIZZA/Existencias_Diarias_Chicago.xlsx
+++ b/CHICAGO DEEP DISH PIZZA/Existencias_Diarias_Chicago.xlsx
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -749,7 +749,7 @@
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Chile Serrano</t>
+          <t>Chile Guajillo</t>
         </is>
       </c>
       <c r="B16" s="11" t="n"/>
@@ -759,7 +759,7 @@
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Chile Guajillo</t>
+          <t>Chile Jalapeño</t>
         </is>
       </c>
       <c r="B17" s="11" t="n"/>
@@ -769,7 +769,7 @@
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Chile Jalapeño</t>
+          <t>Chile Morita</t>
         </is>
       </c>
       <c r="B18" s="11" t="n"/>
@@ -779,7 +779,7 @@
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Chile Morita</t>
+          <t>Chile Serrano</t>
         </is>
       </c>
       <c r="B19" s="11" t="n"/>
@@ -879,7 +879,7 @@
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Pimiento</t>
+          <t>Orégano</t>
         </is>
       </c>
       <c r="B29" s="11" t="n"/>
@@ -889,7 +889,7 @@
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>Orégano</t>
+          <t>Pimiento</t>
         </is>
       </c>
       <c r="B30" s="11" t="n"/>
@@ -951,7 +951,7 @@
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>BBQ</t>
+          <t>Arrachera</t>
         </is>
       </c>
       <c r="B37" s="11" t="n"/>
@@ -961,7 +961,7 @@
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Boneless</t>
+          <t>BBQ</t>
         </is>
       </c>
       <c r="B38" s="11" t="n"/>
@@ -971,7 +971,7 @@
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>Búfalo</t>
+          <t>Boneless</t>
         </is>
       </c>
       <c r="B39" s="11" t="n"/>
@@ -981,7 +981,7 @@
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Calamares</t>
+          <t>Búfalo</t>
         </is>
       </c>
       <c r="B40" s="11" t="n"/>
@@ -991,7 +991,7 @@
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>Camarón</t>
+          <t>Calamares</t>
         </is>
       </c>
       <c r="B41" s="11" t="n"/>
@@ -1001,7 +1001,7 @@
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>Carne Molida</t>
+          <t>Camarón</t>
         </is>
       </c>
       <c r="B42" s="11" t="n"/>
@@ -1011,7 +1011,7 @@
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>Chistorra</t>
+          <t>Carne Molida</t>
         </is>
       </c>
       <c r="B43" s="11" t="n"/>
@@ -1021,7 +1021,7 @@
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Dedos de Queso</t>
+          <t>Chistorra</t>
         </is>
       </c>
       <c r="B44" s="11" t="n"/>
@@ -1031,7 +1031,7 @@
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>Pan</t>
+          <t>Dedos de Queso</t>
         </is>
       </c>
       <c r="B45" s="11" t="n"/>
@@ -1051,7 +1051,7 @@
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>Papas a la Francesa</t>
+          <t>Pan</t>
         </is>
       </c>
       <c r="B47" s="11" t="n"/>
@@ -1061,7 +1061,7 @@
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Pepperoni</t>
+          <t>Papas a la Francesa</t>
         </is>
       </c>
       <c r="B48" s="11" t="n"/>
@@ -1071,7 +1071,7 @@
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>Ranch</t>
+          <t>Pepperoni</t>
         </is>
       </c>
       <c r="B49" s="11" t="n"/>
@@ -1081,7 +1081,7 @@
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>Salami</t>
+          <t>Ranch</t>
         </is>
       </c>
       <c r="B50" s="11" t="n"/>
@@ -1091,7 +1091,7 @@
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>Salchicha Italiana</t>
+          <t>Salami</t>
         </is>
       </c>
       <c r="B51" s="11" t="n"/>
@@ -1101,7 +1101,7 @@
     <row r="52" ht="17" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Tocino</t>
+          <t>Salchicha Italiana</t>
         </is>
       </c>
       <c r="B52" s="11" t="n"/>
@@ -1109,7 +1109,11 @@
       <c r="D52" s="12" t="n"/>
     </row>
     <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="13" t="inlineStr"/>
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>Tocino</t>
+        </is>
+      </c>
       <c r="B53" s="11" t="n"/>
       <c r="C53" s="11" t="n"/>
       <c r="D53" s="14" t="n"/>
@@ -1120,872 +1124,878 @@
       <c r="C54" s="11" t="n"/>
       <c r="D54" s="12" t="n"/>
     </row>
-    <row r="55" ht="19" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="13" t="inlineStr"/>
+      <c r="B55" s="11" t="n"/>
+      <c r="C55" s="11" t="n"/>
+      <c r="D55" s="14" t="n"/>
+    </row>
+    <row r="56" ht="19" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>ALMACÉN</t>
         </is>
       </c>
-      <c r="B55" s="9" t="n"/>
-      <c r="C55" s="9" t="n"/>
-      <c r="D55" s="9" t="n"/>
-    </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="B56" s="9" t="n"/>
+      <c r="C56" s="9" t="n"/>
+      <c r="D56" s="9" t="n"/>
+    </row>
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>Aceite</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="n"/>
-      <c r="C56" s="11" t="n"/>
-      <c r="D56" s="12" t="n"/>
-    </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="13" t="inlineStr">
-        <is>
-          <t>Aceite freidora</t>
         </is>
       </c>
       <c r="B57" s="11" t="n"/>
       <c r="C57" s="11" t="n"/>
-      <c r="D57" s="14" t="n"/>
+      <c r="D57" s="12" t="n"/>
     </row>
     <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="A58" s="13" t="inlineStr">
         <is>
           <t>Aceite de Oliva</t>
         </is>
       </c>
       <c r="B58" s="11" t="n"/>
       <c r="C58" s="11" t="n"/>
-      <c r="D58" s="12" t="n"/>
+      <c r="D58" s="14" t="n"/>
     </row>
     <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="13" t="inlineStr">
-        <is>
-          <t>Aceituna negra</t>
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>Aceite freidora</t>
         </is>
       </c>
       <c r="B59" s="11" t="n"/>
       <c r="C59" s="11" t="n"/>
-      <c r="D59" s="14" t="n"/>
+      <c r="D59" s="12" t="n"/>
     </row>
     <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>Ajo en Polvo</t>
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>Aceituna negra</t>
         </is>
       </c>
       <c r="B60" s="11" t="n"/>
       <c r="C60" s="11" t="n"/>
-      <c r="D60" s="12" t="n"/>
+      <c r="D60" s="14" t="n"/>
     </row>
     <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="13" t="inlineStr">
-        <is>
-          <t>Albahaca Deshidratada</t>
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Ajo en Polvo</t>
         </is>
       </c>
       <c r="B61" s="11" t="n"/>
       <c r="C61" s="11" t="n"/>
-      <c r="D61" s="14" t="n"/>
+      <c r="D61" s="12" t="n"/>
     </row>
     <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>Alcachofa</t>
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>Albahaca Deshidratada</t>
         </is>
       </c>
       <c r="B62" s="11" t="n"/>
       <c r="C62" s="11" t="n"/>
-      <c r="D62" s="12" t="n"/>
+      <c r="D62" s="14" t="n"/>
     </row>
     <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="13" t="inlineStr">
-        <is>
-          <t>Aluminio</t>
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Alcachofa</t>
         </is>
       </c>
       <c r="B63" s="11" t="n"/>
       <c r="C63" s="11" t="n"/>
-      <c r="D63" s="14" t="n"/>
+      <c r="D63" s="12" t="n"/>
     </row>
     <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>Anís Estrella</t>
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>Aluminio</t>
         </is>
       </c>
       <c r="B64" s="11" t="n"/>
       <c r="C64" s="11" t="n"/>
-      <c r="D64" s="12" t="n"/>
+      <c r="D64" s="14" t="n"/>
     </row>
     <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="13" t="inlineStr">
-        <is>
-          <t>Arándanos</t>
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>Anís Estrella</t>
         </is>
       </c>
       <c r="B65" s="11" t="n"/>
       <c r="C65" s="11" t="n"/>
-      <c r="D65" s="14" t="n"/>
+      <c r="D65" s="12" t="n"/>
     </row>
     <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>Azúcar</t>
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>Arándanos</t>
         </is>
       </c>
       <c r="B66" s="11" t="n"/>
       <c r="C66" s="11" t="n"/>
-      <c r="D66" s="12" t="n"/>
+      <c r="D66" s="14" t="n"/>
     </row>
     <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="13" t="inlineStr">
-        <is>
-          <t>Bactericida</t>
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>Azúcar</t>
         </is>
       </c>
       <c r="B67" s="11" t="n"/>
       <c r="C67" s="11" t="n"/>
-      <c r="D67" s="14" t="n"/>
+      <c r="D67" s="12" t="n"/>
     </row>
     <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>Cacahuate</t>
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>Bactericida</t>
         </is>
       </c>
       <c r="B68" s="11" t="n"/>
       <c r="C68" s="11" t="n"/>
-      <c r="D68" s="12" t="n"/>
+      <c r="D68" s="14" t="n"/>
     </row>
     <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="13" t="inlineStr">
-        <is>
-          <t>Cardamomo</t>
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>Cacahuate</t>
         </is>
       </c>
       <c r="B69" s="11" t="n"/>
       <c r="C69" s="11" t="n"/>
-      <c r="D69" s="14" t="n"/>
+      <c r="D69" s="12" t="n"/>
     </row>
     <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="10" t="inlineStr">
-        <is>
-          <t>Catsup</t>
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>Cardamomo</t>
         </is>
       </c>
       <c r="B70" s="11" t="n"/>
       <c r="C70" s="11" t="n"/>
-      <c r="D70" s="12" t="n"/>
+      <c r="D70" s="14" t="n"/>
     </row>
     <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="13" t="inlineStr">
-        <is>
-          <t>Cebolla en Polvo</t>
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>Catsup</t>
         </is>
       </c>
       <c r="B71" s="11" t="n"/>
       <c r="C71" s="11" t="n"/>
-      <c r="D71" s="14" t="n"/>
+      <c r="D71" s="12" t="n"/>
     </row>
     <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="10" t="inlineStr">
-        <is>
-          <t>Chipotle</t>
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>Cebolla en Polvo</t>
         </is>
       </c>
       <c r="B72" s="11" t="n"/>
       <c r="C72" s="11" t="n"/>
-      <c r="D72" s="12" t="n"/>
+      <c r="D72" s="14" t="n"/>
     </row>
     <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="13" t="inlineStr">
-        <is>
-          <t>Chocolate</t>
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>Chipotle</t>
         </is>
       </c>
       <c r="B73" s="11" t="n"/>
       <c r="C73" s="11" t="n"/>
-      <c r="D73" s="14" t="n"/>
+      <c r="D73" s="12" t="n"/>
     </row>
     <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>Clavo</t>
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>Chocolate</t>
         </is>
       </c>
       <c r="B74" s="11" t="n"/>
       <c r="C74" s="11" t="n"/>
-      <c r="D74" s="12" t="n"/>
+      <c r="D74" s="14" t="n"/>
     </row>
     <row r="75" ht="17" customHeight="1">
-      <c r="A75" s="13" t="inlineStr">
-        <is>
-          <t>Condimento Italiano</t>
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>Clavo</t>
         </is>
       </c>
       <c r="B75" s="11" t="n"/>
       <c r="C75" s="11" t="n"/>
-      <c r="D75" s="14" t="n"/>
+      <c r="D75" s="12" t="n"/>
     </row>
     <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>Consomé</t>
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>Condimento Italiano</t>
         </is>
       </c>
       <c r="B76" s="11" t="n"/>
       <c r="C76" s="11" t="n"/>
-      <c r="D76" s="12" t="n"/>
+      <c r="D76" s="14" t="n"/>
     </row>
     <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="13" t="inlineStr">
-        <is>
-          <t>Crema para Batir</t>
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>Consomé</t>
         </is>
       </c>
       <c r="B77" s="11" t="n"/>
       <c r="C77" s="11" t="n"/>
-      <c r="D77" s="14" t="n"/>
+      <c r="D77" s="12" t="n"/>
     </row>
     <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>Espagueti</t>
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>Crema para Batir</t>
         </is>
       </c>
       <c r="B78" s="11" t="n"/>
       <c r="C78" s="11" t="n"/>
-      <c r="D78" s="12" t="n"/>
+      <c r="D78" s="14" t="n"/>
     </row>
     <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="13" t="inlineStr">
-        <is>
-          <t>Frutos rojos</t>
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>Espagueti</t>
         </is>
       </c>
       <c r="B79" s="11" t="n"/>
       <c r="C79" s="11" t="n"/>
-      <c r="D79" s="14" t="n"/>
+      <c r="D79" s="12" t="n"/>
     </row>
     <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>Grenetina</t>
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>Frutos rojos</t>
         </is>
       </c>
       <c r="B80" s="11" t="n"/>
       <c r="C80" s="11" t="n"/>
-      <c r="D80" s="12" t="n"/>
+      <c r="D80" s="14" t="n"/>
     </row>
     <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="13" t="inlineStr">
-        <is>
-          <t>Harina</t>
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Grenetina</t>
         </is>
       </c>
       <c r="B81" s="11" t="n"/>
       <c r="C81" s="11" t="n"/>
-      <c r="D81" s="14" t="n"/>
+      <c r="D81" s="12" t="n"/>
     </row>
     <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="10" t="inlineStr">
-        <is>
-          <t>Harina de arroz</t>
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>Harina</t>
         </is>
       </c>
       <c r="B82" s="11" t="n"/>
       <c r="C82" s="11" t="n"/>
-      <c r="D82" s="12" t="n"/>
+      <c r="D82" s="14" t="n"/>
     </row>
     <row r="83" ht="17" customHeight="1">
-      <c r="A83" s="13" t="inlineStr">
-        <is>
-          <t>Hojaldra</t>
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>Harina de arroz</t>
         </is>
       </c>
       <c r="B83" s="11" t="n"/>
       <c r="C83" s="11" t="n"/>
-      <c r="D83" s="14" t="n"/>
+      <c r="D83" s="12" t="n"/>
     </row>
     <row r="84" ht="17" customHeight="1">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t>Jamón Serrano</t>
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>Hojaldra</t>
         </is>
       </c>
       <c r="B84" s="11" t="n"/>
       <c r="C84" s="11" t="n"/>
-      <c r="D84" s="12" t="n"/>
+      <c r="D84" s="14" t="n"/>
     </row>
     <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="13" t="inlineStr">
-        <is>
-          <t>Leche evaporada</t>
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>Jamón Serrano</t>
         </is>
       </c>
       <c r="B85" s="11" t="n"/>
       <c r="C85" s="11" t="n"/>
-      <c r="D85" s="14" t="n"/>
+      <c r="D85" s="12" t="n"/>
     </row>
     <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="10" t="inlineStr">
+      <c r="A86" s="13" t="inlineStr">
         <is>
           <t>Leche Entera</t>
         </is>
       </c>
       <c r="B86" s="11" t="n"/>
       <c r="C86" s="11" t="n"/>
-      <c r="D86" s="12" t="n"/>
+      <c r="D86" s="14" t="n"/>
     </row>
     <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="13" t="inlineStr">
-        <is>
-          <t>Lemon Pepper</t>
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>Leche evaporada</t>
         </is>
       </c>
       <c r="B87" s="11" t="n"/>
       <c r="C87" s="11" t="n"/>
-      <c r="D87" s="14" t="n"/>
+      <c r="D87" s="12" t="n"/>
     </row>
     <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="10" t="inlineStr">
-        <is>
-          <t>Levadura</t>
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>Lemon Pepper</t>
         </is>
       </c>
       <c r="B88" s="11" t="n"/>
       <c r="C88" s="11" t="n"/>
-      <c r="D88" s="12" t="n"/>
+      <c r="D88" s="14" t="n"/>
     </row>
     <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="13" t="inlineStr">
-        <is>
-          <t>Maizena</t>
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>Levadura</t>
         </is>
       </c>
       <c r="B89" s="11" t="n"/>
       <c r="C89" s="11" t="n"/>
-      <c r="D89" s="14" t="n"/>
+      <c r="D89" s="12" t="n"/>
     </row>
     <row r="90" ht="17" customHeight="1">
-      <c r="A90" s="10" t="inlineStr">
-        <is>
-          <t>Margarina</t>
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>Maizena</t>
         </is>
       </c>
       <c r="B90" s="11" t="n"/>
       <c r="C90" s="11" t="n"/>
-      <c r="D90" s="12" t="n"/>
+      <c r="D90" s="14" t="n"/>
     </row>
     <row r="91" ht="17" customHeight="1">
-      <c r="A91" s="13" t="inlineStr">
-        <is>
-          <t>Mayonesa</t>
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>Margarina</t>
         </is>
       </c>
       <c r="B91" s="11" t="n"/>
       <c r="C91" s="11" t="n"/>
-      <c r="D91" s="14" t="n"/>
+      <c r="D91" s="12" t="n"/>
     </row>
     <row r="92" ht="17" customHeight="1">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>Media crema</t>
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>Mayonesa</t>
         </is>
       </c>
       <c r="B92" s="11" t="n"/>
       <c r="C92" s="11" t="n"/>
-      <c r="D92" s="12" t="n"/>
+      <c r="D92" s="14" t="n"/>
     </row>
     <row r="93" ht="17" customHeight="1">
-      <c r="A93" s="13" t="inlineStr">
-        <is>
-          <t>Miel</t>
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>Media crema</t>
         </is>
       </c>
       <c r="B93" s="11" t="n"/>
       <c r="C93" s="11" t="n"/>
-      <c r="D93" s="14" t="n"/>
+      <c r="D93" s="12" t="n"/>
     </row>
     <row r="94" ht="17" customHeight="1">
-      <c r="A94" s="10" t="inlineStr">
-        <is>
-          <t>Mostaza</t>
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>Miel</t>
         </is>
       </c>
       <c r="B94" s="11" t="n"/>
       <c r="C94" s="11" t="n"/>
-      <c r="D94" s="12" t="n"/>
+      <c r="D94" s="14" t="n"/>
     </row>
     <row r="95" ht="17" customHeight="1">
-      <c r="A95" s="13" t="inlineStr">
-        <is>
-          <t>Nuez Caramelizada</t>
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>Mostaza</t>
         </is>
       </c>
       <c r="B95" s="11" t="n"/>
       <c r="C95" s="11" t="n"/>
-      <c r="D95" s="14" t="n"/>
+      <c r="D95" s="12" t="n"/>
     </row>
     <row r="96" ht="17" customHeight="1">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>Ostiones</t>
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>Nuez Caramelizada</t>
         </is>
       </c>
       <c r="B96" s="11" t="n"/>
       <c r="C96" s="11" t="n"/>
-      <c r="D96" s="12" t="n"/>
+      <c r="D96" s="14" t="n"/>
     </row>
     <row r="97" ht="17" customHeight="1">
-      <c r="A97" s="13" t="inlineStr">
-        <is>
-          <t>Paprika</t>
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>Ostiones</t>
         </is>
       </c>
       <c r="B97" s="11" t="n"/>
       <c r="C97" s="11" t="n"/>
-      <c r="D97" s="14" t="n"/>
+      <c r="D97" s="12" t="n"/>
     </row>
     <row r="98" ht="17" customHeight="1">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>Pimienta trozada</t>
+      <c r="A98" s="13" t="inlineStr">
+        <is>
+          <t>Paprika</t>
         </is>
       </c>
       <c r="B98" s="11" t="n"/>
       <c r="C98" s="11" t="n"/>
-      <c r="D98" s="12" t="n"/>
+      <c r="D98" s="14" t="n"/>
     </row>
     <row r="99" ht="17" customHeight="1">
-      <c r="A99" s="13" t="inlineStr">
-        <is>
-          <t>Pimiento Morrón</t>
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>Pimienta trozada</t>
         </is>
       </c>
       <c r="B99" s="11" t="n"/>
       <c r="C99" s="11" t="n"/>
-      <c r="D99" s="14" t="n"/>
+      <c r="D99" s="12" t="n"/>
     </row>
     <row r="100" ht="17" customHeight="1">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t>Piña</t>
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t>Pimiento Morrón</t>
         </is>
       </c>
       <c r="B100" s="11" t="n"/>
       <c r="C100" s="11" t="n"/>
-      <c r="D100" s="12" t="n"/>
+      <c r="D100" s="14" t="n"/>
     </row>
     <row r="101" ht="17" customHeight="1">
-      <c r="A101" s="13" t="inlineStr">
-        <is>
-          <t>Queso Amarillo</t>
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>Piña</t>
         </is>
       </c>
       <c r="B101" s="11" t="n"/>
       <c r="C101" s="11" t="n"/>
-      <c r="D101" s="14" t="n"/>
+      <c r="D101" s="12" t="n"/>
     </row>
     <row r="102" ht="17" customHeight="1">
-      <c r="A102" s="10" t="inlineStr">
-        <is>
-          <t>Queso Cabra</t>
+      <c r="A102" s="13" t="inlineStr">
+        <is>
+          <t>Queso Amarillo</t>
         </is>
       </c>
       <c r="B102" s="11" t="n"/>
       <c r="C102" s="11" t="n"/>
-      <c r="D102" s="12" t="n"/>
+      <c r="D102" s="14" t="n"/>
     </row>
     <row r="103" ht="17" customHeight="1">
-      <c r="A103" s="13" t="inlineStr">
-        <is>
-          <t>Queso Crema</t>
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>Queso Cabra</t>
         </is>
       </c>
       <c r="B103" s="11" t="n"/>
       <c r="C103" s="11" t="n"/>
-      <c r="D103" s="14" t="n"/>
+      <c r="D103" s="12" t="n"/>
     </row>
     <row r="104" ht="17" customHeight="1">
-      <c r="A104" s="10" t="inlineStr">
-        <is>
-          <t>Queso Mozzarella</t>
+      <c r="A104" s="13" t="inlineStr">
+        <is>
+          <t>Queso Crema</t>
         </is>
       </c>
       <c r="B104" s="11" t="n"/>
       <c r="C104" s="11" t="n"/>
-      <c r="D104" s="12" t="n"/>
+      <c r="D104" s="14" t="n"/>
     </row>
     <row r="105" ht="17" customHeight="1">
-      <c r="A105" s="13" t="inlineStr">
-        <is>
-          <t>Queso Panela</t>
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>Queso Mozzarella</t>
         </is>
       </c>
       <c r="B105" s="11" t="n"/>
       <c r="C105" s="11" t="n"/>
-      <c r="D105" s="14" t="n"/>
+      <c r="D105" s="12" t="n"/>
     </row>
     <row r="106" ht="17" customHeight="1">
-      <c r="A106" s="10" t="inlineStr">
-        <is>
-          <t>Queso Parmesano</t>
+      <c r="A106" s="13" t="inlineStr">
+        <is>
+          <t>Queso Panela</t>
         </is>
       </c>
       <c r="B106" s="11" t="n"/>
       <c r="C106" s="11" t="n"/>
-      <c r="D106" s="12" t="n"/>
+      <c r="D106" s="14" t="n"/>
     </row>
     <row r="107" ht="17" customHeight="1">
-      <c r="A107" s="13" t="inlineStr">
+      <c r="A107" s="10" t="inlineStr">
         <is>
           <t>Queso para Pastas</t>
         </is>
       </c>
       <c r="B107" s="11" t="n"/>
       <c r="C107" s="11" t="n"/>
-      <c r="D107" s="14" t="n"/>
+      <c r="D107" s="12" t="n"/>
     </row>
     <row r="108" ht="17" customHeight="1">
-      <c r="A108" s="10" t="inlineStr">
-        <is>
-          <t>Sal</t>
+      <c r="A108" s="13" t="inlineStr">
+        <is>
+          <t>Queso Parmesano</t>
         </is>
       </c>
       <c r="B108" s="11" t="n"/>
       <c r="C108" s="11" t="n"/>
-      <c r="D108" s="12" t="n"/>
+      <c r="D108" s="14" t="n"/>
     </row>
     <row r="109" ht="17" customHeight="1">
-      <c r="A109" s="13" t="inlineStr">
-        <is>
-          <t>Sal de Mar</t>
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>Sal</t>
         </is>
       </c>
       <c r="B109" s="11" t="n"/>
       <c r="C109" s="11" t="n"/>
-      <c r="D109" s="14" t="n"/>
+      <c r="D109" s="12" t="n"/>
     </row>
     <row r="110" ht="17" customHeight="1">
-      <c r="A110" s="10" t="inlineStr">
-        <is>
-          <t>Salsa Sriracha</t>
+      <c r="A110" s="13" t="inlineStr">
+        <is>
+          <t>Sal de Mar</t>
         </is>
       </c>
       <c r="B110" s="11" t="n"/>
       <c r="C110" s="11" t="n"/>
-      <c r="D110" s="12" t="n"/>
+      <c r="D110" s="14" t="n"/>
     </row>
     <row r="111" ht="17" customHeight="1">
-      <c r="A111" s="13" t="inlineStr">
-        <is>
-          <t>Tomate pelado</t>
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>Salsa Sriracha</t>
         </is>
       </c>
       <c r="B111" s="11" t="n"/>
       <c r="C111" s="11" t="n"/>
-      <c r="D111" s="14" t="n"/>
+      <c r="D111" s="12" t="n"/>
     </row>
     <row r="112" ht="17" customHeight="1">
-      <c r="A112" s="10" t="inlineStr">
+      <c r="A112" s="13" t="inlineStr">
         <is>
           <t>Tomate Deshidratado</t>
         </is>
       </c>
       <c r="B112" s="11" t="n"/>
       <c r="C112" s="11" t="n"/>
-      <c r="D112" s="12" t="n"/>
+      <c r="D112" s="14" t="n"/>
     </row>
     <row r="113" ht="17" customHeight="1">
-      <c r="A113" s="13" t="inlineStr">
-        <is>
-          <t>Vainilla</t>
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>Tomate pelado</t>
         </is>
       </c>
       <c r="B113" s="11" t="n"/>
       <c r="C113" s="11" t="n"/>
-      <c r="D113" s="14" t="n"/>
+      <c r="D113" s="12" t="n"/>
     </row>
     <row r="114" ht="17" customHeight="1">
-      <c r="A114" s="10" t="inlineStr">
-        <is>
-          <t>Vinagre Balsámico</t>
+      <c r="A114" s="13" t="inlineStr">
+        <is>
+          <t>Vainilla</t>
         </is>
       </c>
       <c r="B114" s="11" t="n"/>
       <c r="C114" s="11" t="n"/>
-      <c r="D114" s="12" t="n"/>
+      <c r="D114" s="14" t="n"/>
     </row>
     <row r="115" ht="17" customHeight="1">
-      <c r="A115" s="13" t="inlineStr">
-        <is>
-          <t>Vinagre Blanco</t>
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>Vinagre Balsámico</t>
         </is>
       </c>
       <c r="B115" s="11" t="n"/>
       <c r="C115" s="11" t="n"/>
-      <c r="D115" s="14" t="n"/>
+      <c r="D115" s="12" t="n"/>
     </row>
     <row r="116" ht="17" customHeight="1">
-      <c r="A116" s="10" t="inlineStr">
-        <is>
-          <t>Vino Blanco</t>
+      <c r="A116" s="13" t="inlineStr">
+        <is>
+          <t>Vinagre Blanco</t>
         </is>
       </c>
       <c r="B116" s="11" t="n"/>
       <c r="C116" s="11" t="n"/>
-      <c r="D116" s="12" t="n"/>
+      <c r="D116" s="14" t="n"/>
     </row>
     <row r="117" ht="17" customHeight="1">
-      <c r="A117" s="13" t="inlineStr">
-        <is>
-          <t>Vino Tinto</t>
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>Vino Blanco</t>
         </is>
       </c>
       <c r="B117" s="11" t="n"/>
       <c r="C117" s="11" t="n"/>
-      <c r="D117" s="14" t="n"/>
+      <c r="D117" s="12" t="n"/>
     </row>
     <row r="118" ht="17" customHeight="1">
-      <c r="A118" s="10" t="inlineStr">
-        <is>
-          <t>Vitafil</t>
+      <c r="A118" s="13" t="inlineStr">
+        <is>
+          <t>Vino Tinto</t>
         </is>
       </c>
       <c r="B118" s="11" t="n"/>
       <c r="C118" s="11" t="n"/>
-      <c r="D118" s="12" t="n"/>
+      <c r="D118" s="14" t="n"/>
     </row>
     <row r="119" ht="17" customHeight="1">
-      <c r="A119" s="13" t="inlineStr">
-        <is>
-          <t>Yogurt Natural</t>
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>Vitafil</t>
         </is>
       </c>
       <c r="B119" s="11" t="n"/>
       <c r="C119" s="11" t="n"/>
-      <c r="D119" s="14" t="n"/>
+      <c r="D119" s="12" t="n"/>
     </row>
     <row r="120" ht="17" customHeight="1">
-      <c r="A120" s="10" t="inlineStr"/>
+      <c r="A120" s="13" t="inlineStr">
+        <is>
+          <t>Yogurt Natural</t>
+        </is>
+      </c>
       <c r="B120" s="11" t="n"/>
       <c r="C120" s="11" t="n"/>
-      <c r="D120" s="12" t="n"/>
+      <c r="D120" s="14" t="n"/>
     </row>
     <row r="121" ht="17" customHeight="1">
-      <c r="A121" s="13" t="inlineStr"/>
+      <c r="A121" s="10" t="inlineStr"/>
       <c r="B121" s="11" t="n"/>
       <c r="C121" s="11" t="n"/>
-      <c r="D121" s="14" t="n"/>
-    </row>
-    <row r="122" ht="19" customHeight="1">
-      <c r="A122" s="8" t="inlineStr">
+      <c r="D121" s="12" t="n"/>
+    </row>
+    <row r="122" ht="17" customHeight="1">
+      <c r="A122" s="13" t="inlineStr"/>
+      <c r="B122" s="11" t="n"/>
+      <c r="C122" s="11" t="n"/>
+      <c r="D122" s="14" t="n"/>
+    </row>
+    <row r="123" ht="19" customHeight="1">
+      <c r="A123" s="8" t="inlineStr">
         <is>
           <t>LIMPIEZA</t>
         </is>
       </c>
-      <c r="B122" s="9" t="n"/>
-      <c r="C122" s="9" t="n"/>
-      <c r="D122" s="9" t="n"/>
-    </row>
-    <row r="123" ht="17" customHeight="1">
-      <c r="A123" s="10" t="inlineStr">
+      <c r="B123" s="9" t="n"/>
+      <c r="C123" s="9" t="n"/>
+      <c r="D123" s="9" t="n"/>
+    </row>
+    <row r="124" ht="17" customHeight="1">
+      <c r="A124" s="10" t="inlineStr">
         <is>
           <t>Bolsa camiseta</t>
-        </is>
-      </c>
-      <c r="B123" s="11" t="n"/>
-      <c r="C123" s="11" t="n"/>
-      <c r="D123" s="12" t="n"/>
-    </row>
-    <row r="124" ht="17" customHeight="1">
-      <c r="A124" s="13" t="inlineStr">
-        <is>
-          <t>Bolsas 1/2 k</t>
         </is>
       </c>
       <c r="B124" s="11" t="n"/>
       <c r="C124" s="11" t="n"/>
-      <c r="D124" s="14" t="n"/>
+      <c r="D124" s="12" t="n"/>
     </row>
     <row r="125" ht="17" customHeight="1">
-      <c r="A125" s="10" t="inlineStr">
+      <c r="A125" s="13" t="inlineStr">
         <is>
           <t>Bolsas 1 k</t>
         </is>
       </c>
       <c r="B125" s="11" t="n"/>
       <c r="C125" s="11" t="n"/>
-      <c r="D125" s="12" t="n"/>
+      <c r="D125" s="14" t="n"/>
     </row>
     <row r="126" ht="17" customHeight="1">
-      <c r="A126" s="13" t="inlineStr">
-        <is>
-          <t>Bolsas 3 k</t>
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>Bolsas 1/2 k</t>
         </is>
       </c>
       <c r="B126" s="11" t="n"/>
       <c r="C126" s="11" t="n"/>
-      <c r="D126" s="14" t="n"/>
+      <c r="D126" s="12" t="n"/>
     </row>
     <row r="127" ht="17" customHeight="1">
-      <c r="A127" s="10" t="inlineStr">
-        <is>
-          <t>Bolsas de basura N.</t>
+      <c r="A127" s="13" t="inlineStr">
+        <is>
+          <t>Bolsas 3 k</t>
         </is>
       </c>
       <c r="B127" s="11" t="n"/>
       <c r="C127" s="11" t="n"/>
-      <c r="D127" s="12" t="n"/>
+      <c r="D127" s="14" t="n"/>
     </row>
     <row r="128" ht="17" customHeight="1">
-      <c r="A128" s="13" t="inlineStr">
-        <is>
-          <t>Caja pizza 16</t>
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>Bolsas de basura N.</t>
         </is>
       </c>
       <c r="B128" s="11" t="n"/>
       <c r="C128" s="11" t="n"/>
-      <c r="D128" s="14" t="n"/>
+      <c r="D128" s="12" t="n"/>
     </row>
     <row r="129" ht="17" customHeight="1">
-      <c r="A129" s="10" t="inlineStr">
+      <c r="A129" s="13" t="inlineStr">
         <is>
           <t>Caja pizza 12</t>
         </is>
       </c>
       <c r="B129" s="11" t="n"/>
       <c r="C129" s="11" t="n"/>
-      <c r="D129" s="12" t="n"/>
+      <c r="D129" s="14" t="n"/>
     </row>
     <row r="130" ht="17" customHeight="1">
-      <c r="A130" s="13" t="inlineStr">
-        <is>
-          <t>Cloro</t>
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>Caja pizza 16</t>
         </is>
       </c>
       <c r="B130" s="11" t="n"/>
       <c r="C130" s="11" t="n"/>
-      <c r="D130" s="14" t="n"/>
+      <c r="D130" s="12" t="n"/>
     </row>
     <row r="131" ht="17" customHeight="1">
-      <c r="A131" s="10" t="inlineStr">
-        <is>
-          <t>Desengrasante</t>
+      <c r="A131" s="13" t="inlineStr">
+        <is>
+          <t>Cloro</t>
         </is>
       </c>
       <c r="B131" s="11" t="n"/>
       <c r="C131" s="11" t="n"/>
-      <c r="D131" s="12" t="n"/>
+      <c r="D131" s="14" t="n"/>
     </row>
     <row r="132" ht="17" customHeight="1">
-      <c r="A132" s="13" t="inlineStr">
-        <is>
-          <t>Escoba</t>
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>Desengrasante</t>
         </is>
       </c>
       <c r="B132" s="11" t="n"/>
       <c r="C132" s="11" t="n"/>
-      <c r="D132" s="14" t="n"/>
+      <c r="D132" s="12" t="n"/>
     </row>
     <row r="133" ht="17" customHeight="1">
-      <c r="A133" s="10" t="inlineStr">
-        <is>
-          <t>Fabuloso</t>
+      <c r="A133" s="13" t="inlineStr">
+        <is>
+          <t>Escoba</t>
         </is>
       </c>
       <c r="B133" s="11" t="n"/>
       <c r="C133" s="11" t="n"/>
-      <c r="D133" s="12" t="n"/>
+      <c r="D133" s="14" t="n"/>
     </row>
     <row r="134" ht="17" customHeight="1">
-      <c r="A134" s="13" t="inlineStr">
-        <is>
-          <t>Fibras Esponja</t>
+      <c r="A134" s="10" t="inlineStr">
+        <is>
+          <t>Fabuloso</t>
         </is>
       </c>
       <c r="B134" s="11" t="n"/>
       <c r="C134" s="11" t="n"/>
-      <c r="D134" s="14" t="n"/>
+      <c r="D134" s="12" t="n"/>
     </row>
     <row r="135" ht="17" customHeight="1">
-      <c r="A135" s="10" t="inlineStr">
-        <is>
-          <t>Fibras Metal</t>
+      <c r="A135" s="13" t="inlineStr">
+        <is>
+          <t>Fibras Esponja</t>
         </is>
       </c>
       <c r="B135" s="11" t="n"/>
       <c r="C135" s="11" t="n"/>
-      <c r="D135" s="12" t="n"/>
+      <c r="D135" s="14" t="n"/>
     </row>
     <row r="136" ht="17" customHeight="1">
-      <c r="A136" s="13" t="inlineStr">
-        <is>
-          <t>Franela</t>
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>Fibras Metal</t>
         </is>
       </c>
       <c r="B136" s="11" t="n"/>
       <c r="C136" s="11" t="n"/>
-      <c r="D136" s="14" t="n"/>
+      <c r="D136" s="12" t="n"/>
     </row>
     <row r="137" ht="17" customHeight="1">
-      <c r="A137" s="10" t="inlineStr">
-        <is>
-          <t>Jabón para Trastes</t>
+      <c r="A137" s="13" t="inlineStr">
+        <is>
+          <t>Franela</t>
         </is>
       </c>
       <c r="B137" s="11" t="n"/>
       <c r="C137" s="11" t="n"/>
-      <c r="D137" s="12" t="n"/>
+      <c r="D137" s="14" t="n"/>
     </row>
     <row r="138" ht="17" customHeight="1">
-      <c r="A138" s="13" t="inlineStr">
-        <is>
-          <t>Recogedor</t>
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>Jabón para Trastes</t>
         </is>
       </c>
       <c r="B138" s="11" t="n"/>
       <c r="C138" s="11" t="n"/>
-      <c r="D138" s="14" t="n"/>
+      <c r="D138" s="12" t="n"/>
     </row>
     <row r="139" ht="17" customHeight="1">
-      <c r="A139" s="10" t="inlineStr">
-        <is>
-          <t>Trapeador</t>
+      <c r="A139" s="13" t="inlineStr">
+        <is>
+          <t>Recogedor</t>
         </is>
       </c>
       <c r="B139" s="11" t="n"/>
       <c r="C139" s="11" t="n"/>
-      <c r="D139" s="12" t="n"/>
+      <c r="D139" s="14" t="n"/>
     </row>
     <row r="140" ht="17" customHeight="1">
-      <c r="A140" s="13" t="inlineStr"/>
+      <c r="A140" s="10" t="inlineStr">
+        <is>
+          <t>Trapeador</t>
+        </is>
+      </c>
       <c r="B140" s="11" t="n"/>
       <c r="C140" s="11" t="n"/>
-      <c r="D140" s="14" t="n"/>
+      <c r="D140" s="12" t="n"/>
     </row>
     <row r="141" ht="17" customHeight="1">
-      <c r="A141" s="10" t="inlineStr"/>
+      <c r="A141" s="13" t="inlineStr"/>
       <c r="B141" s="11" t="n"/>
       <c r="C141" s="11" t="n"/>
-      <c r="D141" s="12" t="n"/>
+      <c r="D141" s="14" t="n"/>
+    </row>
+    <row r="142" ht="17" customHeight="1">
+      <c r="A142" s="10" t="inlineStr"/>
+      <c r="B142" s="11" t="n"/>
+      <c r="C142" s="11" t="n"/>
+      <c r="D142" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A122:D122"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="A55:D55"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A123:D123"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
